--- a/database/event/5577/event_5577_evp_summary.xlsx
+++ b/database/event/5577/event_5577_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.082100000000001</v>
+        <v>9.039099999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.573</v>
+        <v>1.5655</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2476</v>
+        <v>3.1573</v>
       </c>
       <c r="E2" t="n">
-        <v>9.082100000000001</v>
+        <v>9.039099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3196</v>
+        <v>5.2766</v>
       </c>
       <c r="G2" t="n">
         <v>3.7625</v>
       </c>
       <c r="H2" t="n">
-        <v>6.038</v>
+        <v>5.9707</v>
       </c>
       <c r="I2" t="n">
         <v>6.1227</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.5716</v>
+        <v>8.4815</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4845</v>
+        <v>1.4689</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0414</v>
+        <v>2.9351</v>
       </c>
       <c r="E3" t="n">
-        <v>8.5716</v>
+        <v>8.4815</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5268</v>
+        <v>4.4367</v>
       </c>
       <c r="G3" t="n">
         <v>4.0448</v>
       </c>
       <c r="H3" t="n">
-        <v>4.795</v>
+        <v>4.6537</v>
       </c>
       <c r="I3" t="n">
         <v>4.9764</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.524100000000001</v>
+        <v>8.4673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4763</v>
+        <v>1.4665</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0222</v>
+        <v>2.9295</v>
       </c>
       <c r="E4" t="n">
-        <v>8.524100000000001</v>
+        <v>8.4673</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0609</v>
+        <v>4.0041</v>
       </c>
       <c r="G4" t="n">
         <v>4.4632</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0644</v>
+        <v>4.0041</v>
       </c>
       <c r="I4" t="n">
         <v>4.1406</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.8928</v>
+        <v>7.8337</v>
       </c>
       <c r="C5" t="n">
-        <v>1.367</v>
+        <v>1.3567</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7672</v>
+        <v>2.677</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8928</v>
+        <v>7.8337</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9812</v>
+        <v>3.9221</v>
       </c>
       <c r="G5" t="n">
         <v>3.9116</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9812</v>
+        <v>3.9221</v>
       </c>
       <c r="I5" t="n">
         <v>4.0558</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.3923</v>
+        <v>7.3368</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2803</v>
+        <v>1.2707</v>
       </c>
       <c r="D6" t="n">
-        <v>2.565</v>
+        <v>2.4791</v>
       </c>
       <c r="E6" t="n">
-        <v>7.3923</v>
+        <v>7.3368</v>
       </c>
       <c r="F6" t="n">
-        <v>5.212</v>
+        <v>5.1565</v>
       </c>
       <c r="G6" t="n">
         <v>2.1803</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8694</v>
+        <v>5.7823</v>
       </c>
       <c r="I6" t="n">
         <v>5.9794</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.9827</v>
+        <v>6.9616</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2094</v>
+        <v>1.2057</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3995</v>
+        <v>2.3296</v>
       </c>
       <c r="E7" t="n">
-        <v>6.9827</v>
+        <v>6.9616</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8309</v>
+        <v>2.8098</v>
       </c>
       <c r="G7" t="n">
         <v>4.1518</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8309</v>
+        <v>2.8098</v>
       </c>
       <c r="I7" t="n">
         <v>2.8573</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.4402</v>
+        <v>6.3187</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1154</v>
+        <v>1.0944</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1803</v>
+        <v>2.0735</v>
       </c>
       <c r="E8" t="n">
-        <v>6.4402</v>
+        <v>6.3187</v>
       </c>
       <c r="F8" t="n">
-        <v>5.5945</v>
+        <v>5.473</v>
       </c>
       <c r="G8" t="n">
         <v>0.8457</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4692</v>
+        <v>6.2786</v>
       </c>
       <c r="I8" t="n">
         <v>6.714</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.2356</v>
+        <v>6.2068</v>
       </c>
       <c r="C9" t="n">
-        <v>1.08</v>
+        <v>1.075</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0977</v>
+        <v>2.0289</v>
       </c>
       <c r="E9" t="n">
-        <v>6.2356</v>
+        <v>6.2068</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8678</v>
+        <v>3.839</v>
       </c>
       <c r="G9" t="n">
         <v>2.3678</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8678</v>
+        <v>3.839</v>
       </c>
       <c r="I9" t="n">
         <v>3.9039</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.2284</v>
+        <v>6.1929</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0787</v>
+        <v>1.0726</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0948</v>
+        <v>2.0233</v>
       </c>
       <c r="E10" t="n">
-        <v>6.2284</v>
+        <v>6.1929</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1866</v>
+        <v>3.1511</v>
       </c>
       <c r="G10" t="n">
         <v>3.0418</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1866</v>
+        <v>3.1511</v>
       </c>
       <c r="I10" t="n">
         <v>3.2313</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.2201</v>
+        <v>5.1979</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9041</v>
+        <v>0.9002</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6874</v>
+        <v>1.6269</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2201</v>
+        <v>5.1979</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4472</v>
+        <v>4.425</v>
       </c>
       <c r="G11" t="n">
         <v>0.7729</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6702</v>
+        <v>4.6354</v>
       </c>
       <c r="I11" t="n">
         <v>4.7137</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.0936</v>
+        <v>5.0689</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8822</v>
+        <v>0.8779</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6363</v>
+        <v>1.5755</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0936</v>
+        <v>5.0689</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2145</v>
+        <v>2.1898</v>
       </c>
       <c r="G12" t="n">
         <v>2.8792</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2145</v>
+        <v>2.1898</v>
       </c>
       <c r="I12" t="n">
         <v>2.2455</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.9617</v>
+        <v>4.9237</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8593</v>
+        <v>0.8528</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5831</v>
+        <v>1.5177</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9617</v>
+        <v>4.9237</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4081</v>
+        <v>3.3701</v>
       </c>
       <c r="G13" t="n">
         <v>1.5536</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4081</v>
+        <v>3.3701</v>
       </c>
       <c r="I13" t="n">
         <v>3.4559</v>
@@ -1054,7 +1054,7 @@
         <v>0.7614</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3546</v>
+        <v>1.3075</v>
       </c>
       <c r="E14" t="n">
         <v>4.3961</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.2845</v>
+        <v>4.2641</v>
       </c>
       <c r="C15" t="n">
-        <v>0.742</v>
+        <v>0.7385</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3095</v>
+        <v>1.2549</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2845</v>
+        <v>4.2641</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7362</v>
+        <v>2.7158</v>
       </c>
       <c r="G15" t="n">
         <v>1.5483</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7362</v>
+        <v>2.7158</v>
       </c>
       <c r="I15" t="n">
         <v>2.7617</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3065</v>
+        <v>3.2443</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5727</v>
+        <v>0.5619</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9144</v>
+        <v>0.8486</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3065</v>
+        <v>3.2443</v>
       </c>
       <c r="F16" t="n">
-        <v>2.114</v>
+        <v>2.0518</v>
       </c>
       <c r="G16" t="n">
         <v>1.1925</v>
       </c>
       <c r="H16" t="n">
-        <v>2.114</v>
+        <v>2.0518</v>
       </c>
       <c r="I16" t="n">
         <v>2.1941</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8733</v>
+        <v>2.8479</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4976</v>
+        <v>0.4932</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.6907</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8733</v>
+        <v>2.8479</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4108</v>
+        <v>3.3854</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5375</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4108</v>
+        <v>3.3854</v>
       </c>
       <c r="I17" t="n">
         <v>3.4426</v>
@@ -1238,7 +1238,7 @@
         <v>0.4441</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.5775</v>
       </c>
       <c r="E18" t="n">
         <v>2.5639</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5617</v>
+        <v>2.5331</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4437</v>
+        <v>0.4387</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6135</v>
+        <v>0.5653</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5617</v>
+        <v>2.5331</v>
       </c>
       <c r="F19" t="n">
-        <v>2.562</v>
+        <v>2.5334</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0003</v>
       </c>
       <c r="H19" t="n">
-        <v>2.562</v>
+        <v>2.5334</v>
       </c>
       <c r="I19" t="n">
         <v>2.5979</v>
@@ -1330,7 +1330,7 @@
         <v>0.4116</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5387</v>
+        <v>0.5028</v>
       </c>
       <c r="E20" t="n">
         <v>2.3764</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2913</v>
+        <v>2.2676</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3968</v>
+        <v>0.3927</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5043</v>
+        <v>0.4595</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2913</v>
+        <v>2.2676</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1785</v>
+        <v>3.1548</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8872</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1785</v>
+        <v>3.1548</v>
       </c>
       <c r="I21" t="n">
         <v>3.2081</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1929</v>
+        <v>2.2054</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3798</v>
+        <v>0.382</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4645</v>
+        <v>0.4347</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1929</v>
+        <v>2.2054</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1229</v>
+        <v>-1.1104</v>
       </c>
       <c r="G22" t="n">
         <v>3.3158</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1229</v>
+        <v>-1.1104</v>
       </c>
       <c r="I22" t="n">
         <v>-1.1387</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1695</v>
+        <v>2.1719</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3757</v>
+        <v>0.3762</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4551</v>
+        <v>0.4214</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1695</v>
+        <v>2.1719</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2181</v>
+        <v>-0.2157</v>
       </c>
       <c r="G23" t="n">
         <v>2.3876</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2181</v>
+        <v>-0.2157</v>
       </c>
       <c r="I23" t="n">
         <v>-0.2212</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7679</v>
+        <v>1.6817</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3062</v>
+        <v>0.2913</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2928</v>
+        <v>0.2261</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7679</v>
+        <v>1.6817</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9253</v>
+        <v>2.8391</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1574</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9253</v>
+        <v>2.8391</v>
       </c>
       <c r="I24" t="n">
         <v>3.036</v>
@@ -1560,7 +1560,7 @@
         <v>0.2381</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1341</v>
+        <v>0.1039</v>
       </c>
       <c r="E25" t="n">
         <v>1.375</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.171</v>
+        <v>1.1457</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2028</v>
+        <v>0.1984</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0517</v>
+        <v>0.0125</v>
       </c>
       <c r="E26" t="n">
-        <v>1.171</v>
+        <v>1.1457</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2941</v>
+        <v>1.1457</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.1231</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2941</v>
+        <v>1.1457</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3809</v>
+        <v>1.1457</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1231</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>416</v>
+        <v>241</v>
       </c>
       <c r="L26" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2578</v>
+        <v>1.1457</v>
       </c>
       <c r="N26" t="n">
-        <v>624</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1457</v>
+        <v>1.1034</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1984</v>
+        <v>0.1911</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0415</v>
+        <v>-0.0043</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1457</v>
+        <v>1.1034</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1457</v>
+        <v>2.2265</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1.1231</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1457</v>
+        <v>2.2265</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1457</v>
+        <v>2.3809</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1.1231</v>
       </c>
       <c r="K27" t="n">
-        <v>241</v>
+        <v>416</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1457</v>
+        <v>1.2578</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>624</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>0.1579</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.053</v>
+        <v>-0.0806</v>
       </c>
       <c r="E28" t="n">
         <v>0.9119</v>
@@ -1744,7 +1744,7 @@
         <v>0.1494</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1003</v>
       </c>
       <c r="E29" t="n">
         <v>0.8626</v>
@@ -1790,7 +1790,7 @@
         <v>0.1387</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0978</v>
+        <v>-0.1248</v>
       </c>
       <c r="E30" t="n">
         <v>0.8008999999999999</v>
@@ -1836,7 +1836,7 @@
         <v>0.1371</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1016</v>
+        <v>-0.1286</v>
       </c>
       <c r="E31" t="n">
         <v>0.7915</v>
@@ -1882,7 +1882,7 @@
         <v>0.1114</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1614</v>
+        <v>-0.1876</v>
       </c>
       <c r="E32" t="n">
         <v>0.6434</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6142</v>
+        <v>0.6063</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1064</v>
+        <v>0.105</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1732</v>
+        <v>-0.2024</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6142</v>
+        <v>0.6063</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7013</v>
       </c>
       <c r="G33" t="n">
         <v>-0.095</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7013</v>
       </c>
       <c r="I33" t="n">
         <v>0.7192</v>
@@ -1974,7 +1974,7 @@
         <v>0.1003</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1874</v>
+        <v>-0.2132</v>
       </c>
       <c r="E34" t="n">
         <v>0.5790999999999999</v>
@@ -2020,7 +2020,7 @@
         <v>0.0669</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2654</v>
+        <v>-0.2901</v>
       </c>
       <c r="E35" t="n">
         <v>0.3861</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3628</v>
+        <v>0.3633</v>
       </c>
       <c r="C36" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0629</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2748</v>
+        <v>-0.2992</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3628</v>
+        <v>0.3633</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0484</v>
+        <v>-0.0479</v>
       </c>
       <c r="G36" t="n">
         <v>0.4112</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0484</v>
+        <v>-0.0479</v>
       </c>
       <c r="I36" t="n">
         <v>-0.0491</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3387</v>
+        <v>0.3313</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0587</v>
+        <v>0.0574</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2845</v>
+        <v>-0.3119</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3387</v>
+        <v>0.3313</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6676</v>
+        <v>0.6602</v>
       </c>
       <c r="G37" t="n">
         <v>-0.3289</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6676</v>
+        <v>0.6602</v>
       </c>
       <c r="I37" t="n">
         <v>0.677</v>
@@ -2158,7 +2158,7 @@
         <v>0.0536</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2964</v>
+        <v>-0.3207</v>
       </c>
       <c r="E38" t="n">
         <v>0.3093</v>
@@ -2204,7 +2204,7 @@
         <v>0.0456</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3151</v>
+        <v>-0.3391</v>
       </c>
       <c r="E39" t="n">
         <v>0.2631</v>
@@ -2250,7 +2250,7 @@
         <v>0.0145</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3875</v>
+        <v>-0.4106</v>
       </c>
       <c r="E40" t="n">
         <v>0.0837</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0552</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0124</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3925</v>
+        <v>-0.4219</v>
       </c>
       <c r="E41" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0552</v>
       </c>
       <c r="F41" t="n">
-        <v>1.102</v>
+        <v>1.0857</v>
       </c>
       <c r="G41" t="n">
         <v>-1.0305</v>
       </c>
       <c r="H41" t="n">
-        <v>1.102</v>
+        <v>1.0857</v>
       </c>
       <c r="I41" t="n">
         <v>1.1227</v>
@@ -2342,7 +2342,7 @@
         <v>-0.0398</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5143</v>
+        <v>-0.5355</v>
       </c>
       <c r="E42" t="n">
         <v>-0.23</v>
@@ -2388,7 +2388,7 @@
         <v>-0.0585</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5577</v>
+        <v>-0.5784</v>
       </c>
       <c r="E43" t="n">
         <v>-0.3375</v>
@@ -2434,7 +2434,7 @@
         <v>-0.0694</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5833</v>
+        <v>-0.6036</v>
       </c>
       <c r="E44" t="n">
         <v>-0.4008</v>
@@ -2480,7 +2480,7 @@
         <v>-0.07480000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5957</v>
+        <v>-0.6159</v>
       </c>
       <c r="E45" t="n">
         <v>-0.4316</v>
@@ -2526,7 +2526,7 @@
         <v>-0.08260000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.614</v>
+        <v>-0.6339</v>
       </c>
       <c r="E46" t="n">
         <v>-0.4769</v>
@@ -2572,7 +2572,7 @@
         <v>-0.0921</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6362</v>
+        <v>-0.6558</v>
       </c>
       <c r="E47" t="n">
         <v>-0.5318000000000001</v>
@@ -2618,7 +2618,7 @@
         <v>-0.1033</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6624</v>
+        <v>-0.6816</v>
       </c>
       <c r="E48" t="n">
         <v>-0.5967</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.6625</v>
+        <v>-0.6663</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1147</v>
+        <v>-0.1154</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7094</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.6625</v>
+        <v>-0.6663</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5117</v>
+        <v>0.5079</v>
       </c>
       <c r="G49" t="n">
         <v>-1.1742</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5117</v>
+        <v>0.5079</v>
       </c>
       <c r="I49" t="n">
         <v>0.5165</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>-0.6893</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.1194</v>
+      </c>
+      <c r="D50" t="n">
         <v>-0.7185</v>
       </c>
-      <c r="C50" t="n">
-        <v>-0.1244</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.7116</v>
-      </c>
       <c r="E50" t="n">
-        <v>-0.7185</v>
+        <v>-0.6893</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.9669</v>
+        <v>-1.9377</v>
       </c>
       <c r="G50" t="n">
         <v>1.2484</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.9669</v>
+        <v>-1.9377</v>
       </c>
       <c r="I50" t="n">
         <v>-2.0038</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.7533</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1302</v>
+        <v>-0.1305</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.725</v>
+        <v>-0.744</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.7533</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2435</v>
+        <v>0.2417</v>
       </c>
       <c r="G51" t="n">
         <v>-0.995</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2435</v>
+        <v>0.2417</v>
       </c>
       <c r="I51" t="n">
         <v>0.2458</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1509</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7734</v>
+        <v>-0.7911</v>
       </c>
       <c r="E52" t="n">
         <v>-0.8714</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1774</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.852</v>
       </c>
       <c r="E53" t="n">
         <v>-1.0244</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0873</v>
+        <v>-1.1016</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1883</v>
+        <v>-0.1908</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8606</v>
+        <v>-0.8828</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.0873</v>
+        <v>-1.1016</v>
       </c>
       <c r="F54" t="n">
-        <v>1.9127</v>
+        <v>1.8984</v>
       </c>
       <c r="G54" t="n">
         <v>-3</v>
       </c>
       <c r="H54" t="n">
-        <v>1.9127</v>
+        <v>1.8984</v>
       </c>
       <c r="I54" t="n">
         <v>1.9305</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2682</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.0469</v>
+        <v>-1.0608</v>
       </c>
       <c r="E55" t="n">
         <v>-1.5485</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.934</v>
+        <v>-1.9266</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.335</v>
+        <v>-0.3337</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.2027</v>
+        <v>-1.2115</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.934</v>
+        <v>-1.9266</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.9925</v>
+        <v>-0.9851</v>
       </c>
       <c r="G56" t="n">
         <v>-0.9415</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.9925</v>
+        <v>-0.9851</v>
       </c>
       <c r="I56" t="n">
         <v>-1.0018</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3381</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.2101</v>
+        <v>-1.2217</v>
       </c>
       <c r="E57" t="n">
         <v>-1.9524</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3573</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2548</v>
+        <v>-1.2658</v>
       </c>
       <c r="E58" t="n">
         <v>-2.0631</v>
@@ -3124,7 +3124,7 @@
         <v>-0.5121</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.6159</v>
+        <v>-1.622</v>
       </c>
       <c r="E59" t="n">
         <v>-2.957</v>
@@ -3170,7 +3170,7 @@
         <v>-0.518</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.6296</v>
+        <v>-1.6354</v>
       </c>
       <c r="E60" t="n">
         <v>-2.9908</v>
@@ -3216,7 +3216,7 @@
         <v>-0.6022999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.8262</v>
+        <v>-1.8293</v>
       </c>
       <c r="E61" t="n">
         <v>-3.4774</v>
